--- a/r4-ELGA-e-Medikation-main/ValueSet-elga-medikationrezeptart.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-elga-medikationrezeptart.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-elga-medikationrezeptart.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-elga-medikationrezeptart.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.40.0.34.10.68 (use: official, )</t>
+    <t>OID:1.2.40.0.34.10.68 (use: official)</t>
   </si>
   <si>
     <t>Version</t>
